--- a/tests/M1-sankalpam.xlsx
+++ b/tests/M1-sankalpam.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="2" max="2"/>
@@ -454,6 +454,7 @@
     <col width="24.140625" customWidth="1" min="7" max="7"/>
     <col width="26.5703125" customWidth="1" min="8" max="8"/>
     <col width="30.42578125" customWidth="1" min="9" max="9"/>
+    <col width="62" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -512,6 +513,11 @@
           <t>Test Type</t>
         </is>
       </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="57.95" customHeight="1">
       <c r="A2" s="3" t="n">
@@ -556,6 +562,11 @@
       </c>
       <c r="J2" s="4" t="inlineStr"/>
       <c r="K2" s="4" t="inlineStr"/>
+      <c r="L2" s="4" t="inlineStr">
+        <is>
+          <t>PASS. build_content.py --check: 0 errors, 0 warnings, 108 names. Flags: 10 VARIANT; 36, 37, 40, 73, 75, 81, 86, 98, 105 CORRECTED; 65, 77, 103 SCRIPT; 108 VARIANT.</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="57.95" customHeight="1">
       <c r="A3" s="3" t="n">
@@ -602,6 +613,11 @@
       </c>
       <c r="J3" s="4" t="inlineStr"/>
       <c r="K3" s="4" t="inlineStr"/>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>PASS. The player opened. My japam showed Ganapati mula mantra, 0 so far, of 10,008, Day 1 of 41.</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="57.95" customHeight="1">
       <c r="A4" s="3" t="n">
@@ -647,6 +663,11 @@
       </c>
       <c r="J4" s="4" t="inlineStr"/>
       <c r="K4" s="4" t="inlineStr"/>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>PASS. On step 3 with no text, Start is not clickable and the form shows Choose what you will chant.</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="57.95" customHeight="1">
       <c r="A5" s="3" t="n">
@@ -692,6 +713,11 @@
       </c>
       <c r="J5" s="4" t="inlineStr"/>
       <c r="K5" s="4" t="inlineStr"/>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>PASS. The reason appears only in About, as “for my mother health · only you see this”. It is not on the card or on Home. The apostrophe did not survive the emulator keyboard.</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="57.95" customHeight="1">
       <c r="A6" s="3" t="n">
@@ -737,6 +763,11 @@
       </c>
       <c r="J6" s="4" t="inlineStr"/>
       <c r="K6" s="4" t="inlineStr"/>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>waiting for audio</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="57.95" customHeight="1">
       <c r="A7" s="3" t="n">
@@ -782,6 +813,11 @@
       </c>
       <c r="J7" s="4" t="inlineStr"/>
       <c r="K7" s="4" t="inlineStr"/>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>waiting for audio</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="57.95" customHeight="1">
       <c r="A8" s="3" t="n">
@@ -827,6 +863,11 @@
       </c>
       <c r="J8" s="4" t="inlineStr"/>
       <c r="K8" s="4" t="inlineStr"/>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>waiting for audio</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="57.95" customHeight="1">
       <c r="A9" s="3" t="n">
@@ -872,6 +913,11 @@
       </c>
       <c r="J9" s="4" t="inlineStr"/>
       <c r="K9" s="4" t="inlineStr"/>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>waiting for audio</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="57.95" customHeight="1">
       <c r="A10" s="3" t="n">
@@ -917,6 +963,11 @@
       </c>
       <c r="J10" s="4" t="inlineStr"/>
       <c r="K10" s="4" t="inlineStr"/>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>waiting for audio</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="57.95" customHeight="1">
       <c r="A11" s="3" t="n">
@@ -962,6 +1013,11 @@
       </c>
       <c r="J11" s="4" t="inlineStr"/>
       <c r="K11" s="4" t="inlineStr"/>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>waiting for audio</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="57.95" customHeight="1">
       <c r="A12" s="3" t="n">
@@ -1007,6 +1063,11 @@
       </c>
       <c r="J12" s="4" t="inlineStr"/>
       <c r="K12" s="4" t="inlineStr"/>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>waiting for audio</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="57.95" customHeight="1">
       <c r="A13" s="3" t="n">
@@ -1052,6 +1113,11 @@
       </c>
       <c r="J13" s="4" t="inlineStr"/>
       <c r="K13" s="4" t="inlineStr"/>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>waiting for audio</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="57.95" customHeight="1">
       <c r="A14" s="3" t="n">
@@ -1097,6 +1163,11 @@
       </c>
       <c r="J14" s="4" t="inlineStr"/>
       <c r="K14" s="4" t="inlineStr"/>
+      <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t>waiting for audio</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="57.95" customHeight="1">
       <c r="A15" s="3" t="n">
@@ -1142,6 +1213,11 @@
       </c>
       <c r="J15" s="4" t="inlineStr"/>
       <c r="K15" s="4" t="inlineStr"/>
+      <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t>waiting for audio</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="57.95" customHeight="1">
       <c r="A16" s="3" t="n">
@@ -1187,6 +1263,11 @@
       </c>
       <c r="J16" s="4" t="inlineStr"/>
       <c r="K16" s="4" t="inlineStr"/>
+      <c r="L16" s="4" t="inlineStr">
+        <is>
+          <t>PASS. Added 3 for Sun 20 Sep on the 11-day aṣṭottaram. About showed that day, 3, and added by hand.</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="57.95" customHeight="1">
       <c r="A17" s="3" t="n">
@@ -1232,6 +1313,11 @@
       </c>
       <c r="J17" s="4" t="inlineStr"/>
       <c r="K17" s="4" t="inlineStr"/>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>PASS. The day chips run from Today back through the start day (Mon 14) and no earlier. At 0 the sheet stays open and the button stays Add 0.</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="57.95" customHeight="1">
       <c r="A18" s="3" t="n">
@@ -1277,6 +1363,11 @@
       </c>
       <c r="J18" s="4" t="inlineStr"/>
       <c r="K18" s="4" t="inlineStr"/>
+      <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t>PASS. After 3 the line was Goal reached · 3 · keep chanting. After 2 more the card showed 5 so far · of 3. Reopening showed Today 5 · Total 5 of 3, and the goal line did not return.</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="57.95" customHeight="1">
       <c r="A19" s="3" t="n">
@@ -1322,6 +1413,11 @@
       </c>
       <c r="J19" s="4" t="inlineStr"/>
       <c r="K19" s="4" t="inlineStr"/>
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t>PASS. With the debug date on 15 Sep the 1-day japam was under Completed: 0 offered · 1 days · ended Mon 14 Sep. No missed-days wording.</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="57.95" customHeight="1">
       <c r="A20" s="3" t="n">
@@ -1367,6 +1463,11 @@
       </c>
       <c r="J20" s="4" t="inlineStr"/>
       <c r="K20" s="4" t="inlineStr"/>
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>PASS. Start again opened step 3 of 3 for Ganesha Ashtottara, goal 108, Other set to 1, and Today as the start. Start was not tapped.</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="57.95" customHeight="1">
       <c r="A21" s="3" t="n">
@@ -1411,6 +1512,11 @@
       </c>
       <c r="J21" s="4" t="inlineStr"/>
       <c r="K21" s="4" t="inlineStr"/>
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t>Debug build: the pack has no audio file. The aṣṭottaram shows Done and no Play. The mantra shows the ring only and no Play. A release APK was not installed.</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="57.95" customHeight="1">
       <c r="A22" s="3" t="n">
@@ -1456,6 +1562,11 @@
       </c>
       <c r="J22" s="4" t="inlineStr"/>
       <c r="K22" s="4" t="inlineStr"/>
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>PASS offline: cold start, the player, a ring tap (88 to 89) and Add 1 by hand all worked, with no connection message. Play is waiting for audio.</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="57.95" customHeight="1">
       <c r="A23" s="3" t="n">
@@ -1501,6 +1612,11 @@
       </c>
       <c r="J23" s="4" t="inlineStr"/>
       <c r="K23" s="4" t="inlineStr"/>
+      <c r="L23" s="4" t="inlineStr">
+        <is>
+          <t>PASS. On 21 Sep, Home and My japam showed the existing totals and Day 8. No missed days, streaks, 0 today, or red.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
